--- a/tarifario_vidaley.xlsx
+++ b/tarifario_vidaley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBBF462-760E-4F7A-9D9E-FE650665F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2958FFD6-A755-446D-B9F9-C6DE0CA2B41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BB5D62E3-C8AA-47A5-AE20-173E8BC9026C}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>Industria, Manufacturera y Metalmecánica</t>
   </si>
   <si>
-    <t>Oficinas, Consultoría y Colegios</t>
-  </si>
-  <si>
     <t>MAPFRE: EMPLEADO</t>
   </si>
   <si>
@@ -136,10 +133,13 @@
     <t>Endoso</t>
   </si>
   <si>
-    <t>Limpieza</t>
-  </si>
-  <si>
     <t>Construcción, Obras y Contratistas</t>
+  </si>
+  <si>
+    <t>Consultoría, Ingeniería y Supervisión (Visita a Obra)</t>
+  </si>
+  <si>
+    <t>Servicios Generales y Limpieza</t>
   </si>
 </sst>
 </file>
@@ -511,8 +511,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -523,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>33</v>
-      </c>
-      <c r="E1" t="s">
-        <v>34</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
@@ -550,18 +561,18 @@
         <v>6</v>
       </c>
       <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -605,7 +616,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -649,7 +660,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -693,7 +704,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -737,7 +748,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -781,7 +792,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1353,7 +1364,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -1397,7 +1408,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1441,7 +1452,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1485,7 +1496,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1529,7 +1540,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -1573,7 +1584,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1881,7 +1892,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -1925,7 +1936,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -1969,7 +1980,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -2013,7 +2024,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -2057,7 +2068,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2101,7 +2112,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2152,30 +2163,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54FA1ED7-4F91-464A-9E24-5CBF8CCB825C}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>0.18</v>
@@ -2192,7 +2206,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -2209,7 +2223,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2226,7 +2240,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -2243,7 +2257,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -2260,7 +2274,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>30</v>
